--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/105.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/105.xlsx
@@ -426,13 +426,13 @@
         <v>-19.44234942387269</v>
       </c>
       <c r="E2">
-        <v>-10.27948863447706</v>
+        <v>-8.970614735092081</v>
       </c>
       <c r="F2">
-        <v>-3.242396663652735</v>
+        <v>-3.344023261730387</v>
       </c>
       <c r="G2">
-        <v>-10.38761244778787</v>
+        <v>-9.672627306580395</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.29857123719259</v>
       </c>
       <c r="E3">
-        <v>-11.24827413588599</v>
+        <v>-9.50826686860076</v>
       </c>
       <c r="F3">
-        <v>-2.929616729499281</v>
+        <v>-3.468854087495258</v>
       </c>
       <c r="G3">
-        <v>-10.20828019592555</v>
+        <v>-9.276490737896745</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.16143681670328</v>
       </c>
       <c r="E4">
-        <v>-11.16042174013719</v>
+        <v>-10.71384174739677</v>
       </c>
       <c r="F4">
-        <v>-2.772610457074872</v>
+        <v>-3.037895946188816</v>
       </c>
       <c r="G4">
-        <v>-10.31258224368583</v>
+        <v>-9.709198903152725</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.07068986716162</v>
       </c>
       <c r="E5">
-        <v>-11.452549069898</v>
+        <v>-11.34108068219919</v>
       </c>
       <c r="F5">
-        <v>-2.632746419683995</v>
+        <v>-3.139438050791382</v>
       </c>
       <c r="G5">
-        <v>-10.0256572617972</v>
+        <v>-10.11872993908827</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.00970185973056</v>
       </c>
       <c r="E6">
-        <v>-12.17599543499337</v>
+        <v>-11.1991537783248</v>
       </c>
       <c r="F6">
-        <v>-2.579384648330456</v>
+        <v>-2.800812225303181</v>
       </c>
       <c r="G6">
-        <v>-10.10821233591</v>
+        <v>-9.407224181242563</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.98528408117365</v>
       </c>
       <c r="E7">
-        <v>-13.5418103665508</v>
+        <v>-11.98597160868351</v>
       </c>
       <c r="F7">
-        <v>-2.241182946952488</v>
+        <v>-2.849212904281353</v>
       </c>
       <c r="G7">
-        <v>-9.71653176152221</v>
+        <v>-9.44998318742779</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.98689872421044</v>
       </c>
       <c r="E8">
-        <v>-13.68006920647898</v>
+        <v>-11.74982074613152</v>
       </c>
       <c r="F8">
-        <v>-2.39328694108713</v>
+        <v>-2.758156274263423</v>
       </c>
       <c r="G8">
-        <v>-9.643772591660108</v>
+        <v>-9.609985163886307</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.9960489363857</v>
       </c>
       <c r="E9">
-        <v>-14.9410816640769</v>
+        <v>-13.37354132937379</v>
       </c>
       <c r="F9">
-        <v>-2.198244522628376</v>
+        <v>-2.215587222573386</v>
       </c>
       <c r="G9">
-        <v>-9.701515126956076</v>
+        <v>-9.537662986035388</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.0092798917525</v>
       </c>
       <c r="E10">
-        <v>-15.43282865656982</v>
+        <v>-15.0009480904583</v>
       </c>
       <c r="F10">
-        <v>-1.954705334572723</v>
+        <v>-2.367430280976146</v>
       </c>
       <c r="G10">
-        <v>-9.539122936618206</v>
+        <v>-9.538536970057756</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.99091297102293</v>
       </c>
       <c r="E11">
-        <v>-16.15890606506365</v>
+        <v>-14.16837908720009</v>
       </c>
       <c r="F11">
-        <v>-1.758378118272227</v>
+        <v>-2.026576147174414</v>
       </c>
       <c r="G11">
-        <v>-9.41878129572016</v>
+        <v>-9.504815753194739</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.9509020357277</v>
       </c>
       <c r="E12">
-        <v>-16.691635747326</v>
+        <v>-15.14693703551757</v>
       </c>
       <c r="F12">
-        <v>-1.330399614513654</v>
+        <v>-1.958892731793875</v>
       </c>
       <c r="G12">
-        <v>-9.270233806827523</v>
+        <v>-8.454992104508756</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.85496533738565</v>
       </c>
       <c r="E13">
-        <v>-17.85837443303222</v>
+        <v>-15.80283668231454</v>
       </c>
       <c r="F13">
-        <v>-1.259003456433767</v>
+        <v>-1.775594078004609</v>
       </c>
       <c r="G13">
-        <v>-8.196643751715111</v>
+        <v>-8.083373436088948</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.72509300291547</v>
       </c>
       <c r="E14">
-        <v>-18.64803614506776</v>
+        <v>-16.37282212023799</v>
       </c>
       <c r="F14">
-        <v>-1.349982219915834</v>
+        <v>-1.460640507786209</v>
       </c>
       <c r="G14">
-        <v>-8.538735664470162</v>
+        <v>-8.064983355618297</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.55221612725364</v>
       </c>
       <c r="E15">
-        <v>-19.26740912051886</v>
+        <v>-17.96705328074231</v>
       </c>
       <c r="F15">
-        <v>-0.7633572762753081</v>
+        <v>-1.326334815668117</v>
       </c>
       <c r="G15">
-        <v>-7.873574233628715</v>
+        <v>-8.219079318834753</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.36037276411817</v>
       </c>
       <c r="E16">
-        <v>-19.6932215314601</v>
+        <v>-18.14860433218382</v>
       </c>
       <c r="F16">
-        <v>-0.679655720426835</v>
+        <v>-0.7121177822077419</v>
       </c>
       <c r="G16">
-        <v>-8.455958783806224</v>
+        <v>-7.195514917366269</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.16658764977324</v>
       </c>
       <c r="E17">
-        <v>-21.05797680009973</v>
+        <v>-20.21617423833988</v>
       </c>
       <c r="F17">
-        <v>-0.07500550210139179</v>
+        <v>-0.5513730876944979</v>
       </c>
       <c r="G17">
-        <v>-8.142274662323661</v>
+        <v>-7.535852240985505</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.98599397730014</v>
       </c>
       <c r="E18">
-        <v>-21.84760681281721</v>
+        <v>-20.24644708708116</v>
       </c>
       <c r="F18">
-        <v>0.04576466665495654</v>
+        <v>-0.2275957479014775</v>
       </c>
       <c r="G18">
-        <v>-7.602354479778384</v>
+        <v>-6.915525528382409</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.84604196496669</v>
       </c>
       <c r="E19">
-        <v>-22.57431367919811</v>
+        <v>-21.13467556436764</v>
       </c>
       <c r="F19">
-        <v>0.5558476339094053</v>
+        <v>0.3142385419022763</v>
       </c>
       <c r="G19">
-        <v>-7.776595112601306</v>
+        <v>-6.952875103156466</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.7379836141152</v>
       </c>
       <c r="E20">
-        <v>-23.22214358531341</v>
+        <v>-21.96223607537337</v>
       </c>
       <c r="F20">
-        <v>0.8130432869676099</v>
+        <v>0.6220151369428214</v>
       </c>
       <c r="G20">
-        <v>-7.574026141598841</v>
+        <v>-7.053396507910897</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.68774583343818</v>
       </c>
       <c r="E21">
-        <v>-23.52851296582834</v>
+        <v>-22.09203572585523</v>
       </c>
       <c r="F21">
-        <v>1.186401729287792</v>
+        <v>0.925583625577145</v>
       </c>
       <c r="G21">
-        <v>-7.140758494146724</v>
+        <v>-7.203092756105661</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.66747359974745</v>
       </c>
       <c r="E22">
-        <v>-24.46829811969215</v>
+        <v>-23.2789306493696</v>
       </c>
       <c r="F22">
-        <v>1.805932739637125</v>
+        <v>1.060622422846715</v>
       </c>
       <c r="G22">
-        <v>-7.238542077740177</v>
+        <v>-6.883641664293688</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.69242266874955</v>
       </c>
       <c r="E23">
-        <v>-25.40557449895572</v>
+        <v>-22.33523742243716</v>
       </c>
       <c r="F23">
-        <v>2.032794406772215</v>
+        <v>1.475049664262891</v>
       </c>
       <c r="G23">
-        <v>-7.950796018877755</v>
+        <v>-7.268174770862194</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.73470449406264</v>
       </c>
       <c r="E24">
-        <v>-25.43364198085526</v>
+        <v>-23.67326110900952</v>
       </c>
       <c r="F24">
-        <v>1.87431612547303</v>
+        <v>1.60220571732742</v>
       </c>
       <c r="G24">
-        <v>-7.780670394160148</v>
+        <v>-7.228223107294268</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.79151659754342</v>
       </c>
       <c r="E25">
-        <v>-25.84775281496068</v>
+        <v>-24.57686828402605</v>
       </c>
       <c r="F25">
-        <v>2.205485815968633</v>
+        <v>1.988528109501415</v>
       </c>
       <c r="G25">
-        <v>-7.82912684921846</v>
+        <v>-6.529330527953189</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-17.84486426993157</v>
       </c>
       <c r="E26">
-        <v>-26.50325395604498</v>
+        <v>-23.82397325245879</v>
       </c>
       <c r="F26">
-        <v>2.197268411332862</v>
+        <v>1.924096036176864</v>
       </c>
       <c r="G26">
-        <v>-8.381944917184738</v>
+        <v>-7.395849270129726</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-17.87794018146711</v>
       </c>
       <c r="E27">
-        <v>-26.99082116702882</v>
+        <v>-23.79347850849114</v>
       </c>
       <c r="F27">
-        <v>2.165169174474381</v>
+        <v>1.971877924705145</v>
       </c>
       <c r="G27">
-        <v>-7.863390995549917</v>
+        <v>-7.468310490893294</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-17.8863500944296</v>
       </c>
       <c r="E28">
-        <v>-25.87597879345049</v>
+        <v>-23.67353734592398</v>
       </c>
       <c r="F28">
-        <v>2.269624647232593</v>
+        <v>1.929639470836398</v>
       </c>
       <c r="G28">
-        <v>-8.060636609325234</v>
+        <v>-7.638068645056042</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-17.84311784181618</v>
       </c>
       <c r="E29">
-        <v>-25.22818964360126</v>
+        <v>-24.06658624741973</v>
       </c>
       <c r="F29">
-        <v>2.18361194633031</v>
+        <v>2.217684354342259</v>
       </c>
       <c r="G29">
-        <v>-7.975373508961304</v>
+        <v>-7.18138219845912</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-17.75834097136977</v>
       </c>
       <c r="E30">
-        <v>-25.54929015006314</v>
+        <v>-23.85635637008764</v>
       </c>
       <c r="F30">
-        <v>2.255163009114519</v>
+        <v>1.901488233019659</v>
       </c>
       <c r="G30">
-        <v>-8.299595096895368</v>
+        <v>-7.321732776596523</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-17.60445958328355</v>
       </c>
       <c r="E31">
-        <v>-25.39135509057163</v>
+        <v>-23.49481659073727</v>
       </c>
       <c r="F31">
-        <v>1.994250471519954</v>
+        <v>2.002613668818618</v>
       </c>
       <c r="G31">
-        <v>-7.96172412970289</v>
+        <v>-7.476649755106718</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-17.40029027980641</v>
       </c>
       <c r="E32">
-        <v>-24.83540792207197</v>
+        <v>-23.70448040881839</v>
       </c>
       <c r="F32">
-        <v>1.89316479735633</v>
+        <v>1.56849116403348</v>
       </c>
       <c r="G32">
-        <v>-7.365375698440735</v>
+        <v>-7.175383489941962</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-17.13162231840164</v>
       </c>
       <c r="E33">
-        <v>-24.19285821664961</v>
+        <v>-22.51269926184975</v>
       </c>
       <c r="F33">
-        <v>1.520815306532758</v>
+        <v>1.423192208112836</v>
       </c>
       <c r="G33">
-        <v>-7.379554764985433</v>
+        <v>-6.758701675641594</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-16.81510802198533</v>
       </c>
       <c r="E34">
-        <v>-24.17370277159717</v>
+        <v>-23.26575731848128</v>
       </c>
       <c r="F34">
-        <v>1.855803770755267</v>
+        <v>1.589535009534199</v>
       </c>
       <c r="G34">
-        <v>-7.449996552970045</v>
+        <v>-6.978833090729892</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.45577563658898</v>
       </c>
       <c r="E35">
-        <v>-23.36665624784619</v>
+        <v>-22.06175382016593</v>
       </c>
       <c r="F35">
-        <v>1.872395969833341</v>
+        <v>1.68916110033409</v>
       </c>
       <c r="G35">
-        <v>-8.405367026875082</v>
+        <v>-6.563746959379452</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-16.06492505033786</v>
       </c>
       <c r="E36">
-        <v>-23.34141000525342</v>
+        <v>-20.98942928904562</v>
       </c>
       <c r="F36">
-        <v>1.569453726955534</v>
+        <v>1.303201533082522</v>
       </c>
       <c r="G36">
-        <v>-7.327840733116478</v>
+        <v>-7.096642164290397</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.66077726541964</v>
       </c>
       <c r="E37">
-        <v>-22.71928824607967</v>
+        <v>-21.01712996455054</v>
       </c>
       <c r="F37">
-        <v>1.586877606906018</v>
+        <v>1.16244534399883</v>
       </c>
       <c r="G37">
-        <v>-7.089517870289884</v>
+        <v>-6.551835616529154</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.24417828790072</v>
       </c>
       <c r="E38">
-        <v>-22.83475980480126</v>
+        <v>-21.43524849815276</v>
       </c>
       <c r="F38">
-        <v>1.741523860599852</v>
+        <v>1.064845439866187</v>
       </c>
       <c r="G38">
-        <v>-7.130270685878313</v>
+        <v>-6.497883655875652</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.8405362920135</v>
       </c>
       <c r="E39">
-        <v>-21.9917707828514</v>
+        <v>-20.53898197950265</v>
       </c>
       <c r="F39">
-        <v>1.307984526466286</v>
+        <v>1.114428199128154</v>
       </c>
       <c r="G39">
-        <v>-6.290246239652563</v>
+        <v>-5.790333999949379</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.43613116327518</v>
       </c>
       <c r="E40">
-        <v>-21.86202547405763</v>
+        <v>-19.95591830864506</v>
       </c>
       <c r="F40">
-        <v>1.568868899569157</v>
+        <v>0.7546235042525775</v>
       </c>
       <c r="G40">
-        <v>-6.175416657077403</v>
+        <v>-6.047887821813599</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.05140369590617</v>
       </c>
       <c r="E41">
-        <v>-20.89351620956317</v>
+        <v>-19.06617732104001</v>
       </c>
       <c r="F41">
-        <v>1.229788300376819</v>
+        <v>0.8788537636504193</v>
       </c>
       <c r="G41">
-        <v>-6.32664568785685</v>
+        <v>-5.359032816547589</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.6698581576945</v>
       </c>
       <c r="E42">
-        <v>-19.90754062082112</v>
+        <v>-19.67575067873851</v>
       </c>
       <c r="F42">
-        <v>0.917742299742245</v>
+        <v>0.7724499707608228</v>
       </c>
       <c r="G42">
-        <v>-5.707543877103284</v>
+        <v>-5.719763100688735</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.30258297481835</v>
       </c>
       <c r="E43">
-        <v>-20.3163169125455</v>
+        <v>-18.72453112800532</v>
       </c>
       <c r="F43">
-        <v>1.159953614851209</v>
+        <v>0.5955835898542948</v>
       </c>
       <c r="G43">
-        <v>-6.061514027253239</v>
+        <v>-5.29339131959492</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.94003979882947</v>
       </c>
       <c r="E44">
-        <v>-19.49643216498278</v>
+        <v>-18.42844591196182</v>
       </c>
       <c r="F44">
-        <v>0.7308294789745645</v>
+        <v>0.442406859933027</v>
       </c>
       <c r="G44">
-        <v>-5.409482220020543</v>
+        <v>-4.733872707457158</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.58136731120548</v>
       </c>
       <c r="E45">
-        <v>-18.94659843639347</v>
+        <v>-17.69900384728028</v>
       </c>
       <c r="F45">
-        <v>0.8133299020889785</v>
+        <v>0.2864882339084929</v>
       </c>
       <c r="G45">
-        <v>-5.447543562085543</v>
+        <v>-4.649493522752214</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.2259905924541</v>
       </c>
       <c r="E46">
-        <v>-19.13522296423496</v>
+        <v>-16.06786109513944</v>
       </c>
       <c r="F46">
-        <v>0.5806829170127373</v>
+        <v>0.228719547972061</v>
       </c>
       <c r="G46">
-        <v>-5.320948300663813</v>
+        <v>-4.583345512332036</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.86321997495006</v>
       </c>
       <c r="E47">
-        <v>-18.40534163757468</v>
+        <v>-16.10690559803357</v>
       </c>
       <c r="F47">
-        <v>0.4320920290333676</v>
+        <v>0.1192822736534127</v>
       </c>
       <c r="G47">
-        <v>-4.734024992551964</v>
+        <v>-4.054605042072877</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.50173595970254</v>
       </c>
       <c r="E48">
-        <v>-17.96851144937278</v>
+        <v>-16.32406856907141</v>
       </c>
       <c r="F48">
-        <v>0.1668529284939799</v>
+        <v>0.2409512210417984</v>
       </c>
       <c r="G48">
-        <v>-4.397968204315006</v>
+        <v>-3.626773310396244</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.12522470255573</v>
       </c>
       <c r="E49">
-        <v>-17.24775952631196</v>
+        <v>-15.8388244652535</v>
       </c>
       <c r="F49">
-        <v>0.07720783653042017</v>
+        <v>-0.3922014628791701</v>
       </c>
       <c r="G49">
-        <v>-5.624204203697672</v>
+        <v>-3.955801810453329</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.74940443154296</v>
       </c>
       <c r="E50">
-        <v>-17.03146149380959</v>
+        <v>-15.5054925504969</v>
       </c>
       <c r="F50">
-        <v>-0.0803534420538654</v>
+        <v>-0.5071192159347399</v>
       </c>
       <c r="G50">
-        <v>-5.285952523768177</v>
+        <v>-4.272058225819905</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.36315106502261</v>
       </c>
       <c r="E51">
-        <v>-16.36249267102649</v>
+        <v>-15.12872804153273</v>
       </c>
       <c r="F51">
-        <v>-0.1042286473373528</v>
+        <v>-0.5754810642181719</v>
       </c>
       <c r="G51">
-        <v>-5.111357662572554</v>
+        <v>-3.918578036409763</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.98149405431832</v>
       </c>
       <c r="E52">
-        <v>-15.60753718378574</v>
+        <v>-14.29395819990679</v>
       </c>
       <c r="F52">
-        <v>-0.0840148259742392</v>
+        <v>-0.9155540475590641</v>
       </c>
       <c r="G52">
-        <v>-5.307908061784624</v>
+        <v>-3.902068345805418</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.602701002915357</v>
       </c>
       <c r="E53">
-        <v>-15.02595885240266</v>
+        <v>-14.23463971888032</v>
       </c>
       <c r="F53">
-        <v>-0.4461994203980587</v>
+        <v>-0.7875050144343165</v>
       </c>
       <c r="G53">
-        <v>-5.022932991218621</v>
+        <v>-3.784550600252369</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.234800920890684</v>
       </c>
       <c r="E54">
-        <v>-15.00373310197302</v>
+        <v>-13.78320520200368</v>
       </c>
       <c r="F54">
-        <v>-0.4616882340956038</v>
+        <v>-0.7828529031001945</v>
       </c>
       <c r="G54">
-        <v>-5.038532281799667</v>
+        <v>-4.115403210901593</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.882709768319563</v>
       </c>
       <c r="E55">
-        <v>-15.14575510380157</v>
+        <v>-13.42467232939439</v>
       </c>
       <c r="F55">
-        <v>-0.4642346354918095</v>
+        <v>-0.4615639789851839</v>
       </c>
       <c r="G55">
-        <v>-4.932833183821816</v>
+        <v>-3.747518837850082</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.544516120877752</v>
       </c>
       <c r="E56">
-        <v>-13.5186653358976</v>
+        <v>-13.23612478561103</v>
       </c>
       <c r="F56">
-        <v>-0.6316261500451168</v>
+        <v>-0.7769284194353725</v>
       </c>
       <c r="G56">
-        <v>-5.782041083373504</v>
+        <v>-3.903313110928184</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.229889947599004</v>
       </c>
       <c r="E57">
-        <v>-13.60183076104846</v>
+        <v>-12.36764045499798</v>
       </c>
       <c r="F57">
-        <v>-0.6891711767827928</v>
+        <v>-0.882662891463507</v>
       </c>
       <c r="G57">
-        <v>-5.220138878447466</v>
+        <v>-3.885472581017052</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.927174679191403</v>
       </c>
       <c r="E58">
-        <v>-13.83892354619405</v>
+        <v>-11.68773536748636</v>
       </c>
       <c r="F58">
-        <v>-0.2993315366165119</v>
+        <v>-1.100340449203758</v>
       </c>
       <c r="G58">
-        <v>-5.868810481957802</v>
+        <v>-4.548710584900181</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.647733437821866</v>
       </c>
       <c r="E59">
-        <v>-13.13273519554191</v>
+        <v>-11.25578687426472</v>
       </c>
       <c r="F59">
-        <v>-0.6320105125200157</v>
+        <v>-0.890929998143446</v>
       </c>
       <c r="G59">
-        <v>-5.296665449133259</v>
+        <v>-4.582683403224181</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.378700807750489</v>
       </c>
       <c r="E60">
-        <v>-13.14088192028171</v>
+        <v>-11.48552088914784</v>
       </c>
       <c r="F60">
-        <v>-0.7346700847489585</v>
+        <v>-0.9783061917907379</v>
       </c>
       <c r="G60">
-        <v>-5.656515128160959</v>
+        <v>-3.83287794403465</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.126056299064126</v>
       </c>
       <c r="E61">
-        <v>-13.06822255482864</v>
+        <v>-11.37959988210843</v>
       </c>
       <c r="F61">
-        <v>-0.9295178368680554</v>
+        <v>-1.049576438025399</v>
       </c>
       <c r="G61">
-        <v>-6.052280915744211</v>
+        <v>-4.360165084802069</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.88050260432605</v>
       </c>
       <c r="E62">
-        <v>-12.53564684068255</v>
+        <v>-11.65000865052846</v>
       </c>
       <c r="F62">
-        <v>-1.038685891780794</v>
+        <v>-1.11340794498292</v>
       </c>
       <c r="G62">
-        <v>-5.9301383380728</v>
+        <v>-4.680655687913373</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.64125103565675</v>
       </c>
       <c r="E63">
-        <v>-11.71040037989475</v>
+        <v>-11.53204190262864</v>
       </c>
       <c r="F63">
-        <v>-1.031818726011586</v>
+        <v>-1.062253772757842</v>
       </c>
       <c r="G63">
-        <v>-5.678384591993384</v>
+        <v>-4.576217907785985</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.404919153692578</v>
       </c>
       <c r="E64">
-        <v>-11.24063007176105</v>
+        <v>-10.87514146307598</v>
       </c>
       <c r="F64">
-        <v>-1.080896181157845</v>
+        <v>-1.120695921392751</v>
       </c>
       <c r="G64">
-        <v>-5.934203687995026</v>
+        <v>-4.698764372013186</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.166391015942849</v>
       </c>
       <c r="E65">
-        <v>-11.76294426380575</v>
+        <v>-10.3353609467837</v>
       </c>
       <c r="F65">
-        <v>-1.348854811880624</v>
+        <v>-1.053859925865275</v>
       </c>
       <c r="G65">
-        <v>-6.053909704149532</v>
+        <v>-4.304541298651234</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.929549129849387</v>
       </c>
       <c r="E66">
-        <v>-11.60231023380566</v>
+        <v>-10.67255564986884</v>
       </c>
       <c r="F66">
-        <v>-1.240038813114075</v>
+        <v>-1.385589592725171</v>
       </c>
       <c r="G66">
-        <v>-5.633093018470615</v>
+        <v>-4.122424877990387</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.68685129184963</v>
       </c>
       <c r="E67">
-        <v>-11.69752139981693</v>
+        <v>-10.9211462305199</v>
       </c>
       <c r="F67">
-        <v>-1.35932537585201</v>
+        <v>-1.316513691740526</v>
       </c>
       <c r="G67">
-        <v>-5.900459297313234</v>
+        <v>-4.376949550686174</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.446925396436868</v>
       </c>
       <c r="E68">
-        <v>-10.51961549720779</v>
+        <v>-10.59751430708773</v>
       </c>
       <c r="F68">
-        <v>-1.528732308296328</v>
+        <v>-1.823393362248349</v>
       </c>
       <c r="G68">
-        <v>-5.767120454628009</v>
+        <v>-4.053906516964092</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.203486748614533</v>
       </c>
       <c r="E69">
-        <v>-10.78921366878044</v>
+        <v>-10.37508472077898</v>
       </c>
       <c r="F69">
-        <v>-1.304981160758751</v>
+        <v>-1.600441589254473</v>
       </c>
       <c r="G69">
-        <v>-5.132108162012706</v>
+        <v>-4.414411684008567</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.964873342248358</v>
       </c>
       <c r="E70">
-        <v>-11.50291475781131</v>
+        <v>-10.37754821063916</v>
       </c>
       <c r="F70">
-        <v>-1.5606807822875</v>
+        <v>-1.633993782537464</v>
       </c>
       <c r="G70">
-        <v>-5.568404958633256</v>
+        <v>-4.165756608553908</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.728490869547797</v>
       </c>
       <c r="E71">
-        <v>-11.17663367708465</v>
+        <v>-10.84448822251806</v>
       </c>
       <c r="F71">
-        <v>-1.417672262235596</v>
+        <v>-1.79009630612542</v>
       </c>
       <c r="G71">
-        <v>-4.98064739304551</v>
+        <v>-3.949680611751216</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.498337669223584</v>
       </c>
       <c r="E72">
-        <v>-11.44531256843374</v>
+        <v>-11.1047532091609</v>
       </c>
       <c r="F72">
-        <v>-1.457065274075726</v>
+        <v>-1.617487733669281</v>
       </c>
       <c r="G72">
-        <v>-4.891746003133922</v>
+        <v>-4.42497894536992</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.277225999407231</v>
       </c>
       <c r="E73">
-        <v>-11.51951161504942</v>
+        <v>-11.18963945443468</v>
       </c>
       <c r="F73">
-        <v>-1.487099390999028</v>
+        <v>-1.774238868933629</v>
       </c>
       <c r="G73">
-        <v>-4.417291858627732</v>
+        <v>-3.930790638904135</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.065123209931909</v>
       </c>
       <c r="E74">
-        <v>-12.63309960132762</v>
+        <v>-11.92206125501326</v>
       </c>
       <c r="F74">
-        <v>-1.609810424580135</v>
+        <v>-2.345897698707776</v>
       </c>
       <c r="G74">
-        <v>-4.36697156643081</v>
+        <v>-4.107298995421456</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.867330896819108</v>
       </c>
       <c r="E75">
-        <v>-11.9817148431163</v>
+        <v>-10.82771475479365</v>
       </c>
       <c r="F75">
-        <v>-1.812624586011955</v>
+        <v>-2.14335689851888</v>
       </c>
       <c r="G75">
-        <v>-4.062639736096688</v>
+        <v>-3.414312429322437</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.680205162045998</v>
       </c>
       <c r="E76">
-        <v>-12.60039496204423</v>
+        <v>-11.7728344510385</v>
       </c>
       <c r="F76">
-        <v>-1.989812373470769</v>
+        <v>-2.360858014002335</v>
       </c>
       <c r="G76">
-        <v>-3.911685480597001</v>
+        <v>-3.738408216526008</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.510838466552084</v>
       </c>
       <c r="E77">
-        <v>-12.49281653351801</v>
+        <v>-11.59828894888685</v>
       </c>
       <c r="F77">
-        <v>-1.811186540200695</v>
+        <v>-2.320099852682391</v>
       </c>
       <c r="G77">
-        <v>-3.463930885865034</v>
+        <v>-3.222515973504761</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.354766914432008</v>
       </c>
       <c r="E78">
-        <v>-12.93755796581132</v>
+        <v>-12.70828132680296</v>
       </c>
       <c r="F78">
-        <v>-2.224053137429997</v>
+        <v>-2.347183324916921</v>
       </c>
       <c r="G78">
-        <v>-3.370861519119503</v>
+        <v>-2.874614053328291</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.218611257156919</v>
       </c>
       <c r="E79">
-        <v>-13.46469498267418</v>
+        <v>-12.97140378054464</v>
       </c>
       <c r="F79">
-        <v>-2.114348300440244</v>
+        <v>-2.538590867212192</v>
       </c>
       <c r="G79">
-        <v>-2.963896155976895</v>
+        <v>-1.948210852891878</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.10117980022009</v>
       </c>
       <c r="E80">
-        <v>-13.81330144025865</v>
+        <v>-13.72712910836669</v>
       </c>
       <c r="F80">
-        <v>-2.307860724306028</v>
+        <v>-2.599439423152232</v>
       </c>
       <c r="G80">
-        <v>-2.678586720311426</v>
+        <v>-2.408697805767882</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.006191834801304</v>
       </c>
       <c r="E81">
-        <v>-14.42040677962297</v>
+        <v>-14.22473141775154</v>
       </c>
       <c r="F81">
-        <v>-2.463229314375104</v>
+        <v>-2.563779034829116</v>
       </c>
       <c r="G81">
-        <v>-2.453413344366818</v>
+        <v>-2.123858467568989</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.936849343371169</v>
       </c>
       <c r="E82">
-        <v>-15.47502497737329</v>
+        <v>-14.99035598975436</v>
       </c>
       <c r="F82">
-        <v>-2.452246819348788</v>
+        <v>-2.923233330293308</v>
       </c>
       <c r="G82">
-        <v>-2.080731990828903</v>
+        <v>-1.978297090752774</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.893877670321193</v>
       </c>
       <c r="E83">
-        <v>-15.86373560076969</v>
+        <v>-15.55962592878459</v>
       </c>
       <c r="F83">
-        <v>-2.435389542701818</v>
+        <v>-3.005575535233787</v>
       </c>
       <c r="G83">
-        <v>-1.623274187121332</v>
+        <v>-1.170133334796971</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.885711165309761</v>
       </c>
       <c r="E84">
-        <v>-17.33012341156347</v>
+        <v>-16.73093384476456</v>
       </c>
       <c r="F84">
-        <v>-2.808891292582684</v>
+        <v>-3.204571751306104</v>
       </c>
       <c r="G84">
-        <v>-1.608810413660256</v>
+        <v>-1.544059453457651</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.910661431083143</v>
       </c>
       <c r="E85">
-        <v>-17.7715137730911</v>
+        <v>-17.1356662092001</v>
       </c>
       <c r="F85">
-        <v>-2.646604177965427</v>
+        <v>-3.261551831475071</v>
       </c>
       <c r="G85">
-        <v>-1.348932588827468</v>
+        <v>-1.467539503862937</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.981290099410525</v>
       </c>
       <c r="E86">
-        <v>-19.23872123768026</v>
+        <v>-18.87940946754166</v>
       </c>
       <c r="F86">
-        <v>-3.059496454584216</v>
+        <v>-3.338533670952035</v>
       </c>
       <c r="G86">
-        <v>-1.372742032345907</v>
+        <v>-1.248831623356525</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.097927693395681</v>
       </c>
       <c r="E87">
-        <v>-20.25999628131211</v>
+        <v>-19.10698792879713</v>
       </c>
       <c r="F87">
-        <v>-3.307092986178779</v>
+        <v>-3.159155680080219</v>
       </c>
       <c r="G87">
-        <v>-1.580124536562471</v>
+        <v>-1.141722232978945</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.272667435313919</v>
       </c>
       <c r="E88">
-        <v>-21.9219326567051</v>
+        <v>-21.07889382154116</v>
       </c>
       <c r="F88">
-        <v>-3.224235536713759</v>
+        <v>-3.50363143616699</v>
       </c>
       <c r="G88">
-        <v>-1.546479462246859</v>
+        <v>-1.119478677500582</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.512405197321608</v>
       </c>
       <c r="E89">
-        <v>-22.60026636373607</v>
+        <v>-21.75613616633628</v>
       </c>
       <c r="F89">
-        <v>-3.281126981570626</v>
+        <v>-3.832885941227321</v>
       </c>
       <c r="G89">
-        <v>-1.410892759140468</v>
+        <v>-0.8211124502282272</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.825135390391726</v>
       </c>
       <c r="E90">
-        <v>-24.45552329451652</v>
+        <v>-24.00305175709212</v>
       </c>
       <c r="F90">
-        <v>-3.783898778127967</v>
+        <v>-3.503736638827146</v>
       </c>
       <c r="G90">
-        <v>-1.626756881028645</v>
+        <v>-1.007684865184933</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.223091446875301</v>
       </c>
       <c r="E91">
-        <v>-25.76475947182211</v>
+        <v>-25.75285411365594</v>
       </c>
       <c r="F91">
-        <v>-3.660753680027792</v>
+        <v>-3.946988580758536</v>
       </c>
       <c r="G91">
-        <v>-2.18290535780743</v>
+        <v>-1.352716542378855</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.705809005744834</v>
       </c>
       <c r="E92">
-        <v>-27.37958613211331</v>
+        <v>-26.66012029567068</v>
       </c>
       <c r="F92">
-        <v>-3.593274871395745</v>
+        <v>-3.795968091186755</v>
       </c>
       <c r="G92">
-        <v>-1.781759933722862</v>
+        <v>-1.297053029681549</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.287706664246311</v>
       </c>
       <c r="E93">
-        <v>-29.15095308190167</v>
+        <v>-28.81035749483676</v>
       </c>
       <c r="F93">
-        <v>-3.385410153909056</v>
+        <v>-4.12773586294718</v>
       </c>
       <c r="G93">
-        <v>-1.894003980231851</v>
+        <v>-2.094295295903297</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.957381395985551</v>
       </c>
       <c r="E94">
-        <v>-31.68965183839373</v>
+        <v>-30.33901635171001</v>
       </c>
       <c r="F94">
-        <v>-3.534264462722516</v>
+        <v>-4.270760121979737</v>
       </c>
       <c r="G94">
-        <v>-2.668936480064451</v>
+        <v>-2.438396709800684</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.719835774042697</v>
       </c>
       <c r="E95">
-        <v>-33.65179207694021</v>
+        <v>-33.04081489229934</v>
       </c>
       <c r="F95">
-        <v>-3.490852212244002</v>
+        <v>-4.282849315856192</v>
       </c>
       <c r="G95">
-        <v>-3.161251017755008</v>
+        <v>-2.490110741669639</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.5645437325814</v>
       </c>
       <c r="E96">
-        <v>-35.5200661062557</v>
+        <v>-35.28102834152382</v>
       </c>
       <c r="F96">
-        <v>-3.776595891104886</v>
+        <v>-3.952473201332471</v>
       </c>
       <c r="G96">
-        <v>-3.493844975357888</v>
+        <v>-3.33675958951947</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.471054005090998</v>
       </c>
       <c r="E97">
-        <v>-37.98994790749021</v>
+        <v>-36.58336991715274</v>
       </c>
       <c r="F97">
-        <v>-3.576027433702056</v>
+        <v>-4.214429481854565</v>
       </c>
       <c r="G97">
-        <v>-4.075729633158967</v>
+        <v>-3.106415141442521</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.443260787801654</v>
       </c>
       <c r="E98">
-        <v>-40.01876539732563</v>
+        <v>-39.65817433327986</v>
       </c>
       <c r="F98">
-        <v>-3.439524911231739</v>
+        <v>-4.183186776890579</v>
       </c>
       <c r="G98">
-        <v>-4.520855654732753</v>
+        <v>-3.97074230247206</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.42560207529231</v>
       </c>
       <c r="E99">
-        <v>-42.75940239524174</v>
+        <v>-41.83014594344576</v>
       </c>
       <c r="F99">
-        <v>-3.478734025508448</v>
+        <v>-4.43030037028931</v>
       </c>
       <c r="G99">
-        <v>-5.09489100906022</v>
+        <v>-4.31173842465361</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.46014972914087</v>
       </c>
       <c r="E100">
-        <v>-44.95465036180706</v>
+        <v>-44.21042509372749</v>
       </c>
       <c r="F100">
-        <v>-3.657735109211991</v>
+        <v>-4.343743432003388</v>
       </c>
       <c r="G100">
-        <v>-5.483605334644825</v>
+        <v>-4.658173773156182</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.43306569999095</v>
       </c>
       <c r="E101">
-        <v>-47.05005679768828</v>
+        <v>-45.91397135253997</v>
       </c>
       <c r="F101">
-        <v>-3.474344506641014</v>
+        <v>-4.537022256261582</v>
       </c>
       <c r="G101">
-        <v>-5.753255889909541</v>
+        <v>-5.793459154938451</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.49226862571326</v>
       </c>
       <c r="E102">
-        <v>-49.20944377858686</v>
+        <v>-48.44646043904901</v>
       </c>
       <c r="F102">
-        <v>-3.378878476937982</v>
+        <v>-4.333990234202826</v>
       </c>
       <c r="G102">
-        <v>-6.410329657998547</v>
+        <v>-5.623902944053598</v>
       </c>
     </row>
   </sheetData>
